--- a/backend/data/syllabus/UnitChapter_List__CBSE.xlsx
+++ b/backend/data/syllabus/UnitChapter_List__CBSE.xlsx
@@ -17,10 +17,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={3e9cbbfc-2fbe-4d04-a43d-71016acf410c}</author>
+    <author>tc={ae5cab91-4a47-4fb0-885d-5f477d8f6cf1}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{3e9cbbfc-2fbe-4d04-a43d-71016acf410c}" ref="A45">
+    <comment authorId="0" xr:uid="{ae5cab91-4a47-4fb0-885d-5f477d8f6cf1}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="447">
   <si>
     <t>Subject</t>
   </si>
@@ -48,181 +48,244 @@
     <t>Science</t>
   </si>
   <si>
+    <t>Atomic Structure &amp; Language of Chemistry (08_CBSE)</t>
+  </si>
+  <si>
+    <t>Exploring the Investigative World of Science</t>
+  </si>
+  <si>
+    <t>Microorganisms (08_CBSE)</t>
+  </si>
+  <si>
+    <t>The Invisible Living World: Beyond Our Naked Eye</t>
+  </si>
+  <si>
     <t>Thermodynamics (09_CBSE)</t>
   </si>
   <si>
+    <t>Exploration: Entering the World of Secondary Science</t>
+  </si>
+  <si>
+    <t>Optics (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Health &amp; Hygiene (08_CBSE)</t>
+  </si>
+  <si>
+    <t>Light – Reflection and Refraction</t>
+  </si>
+  <si>
+    <t>Health: The Ultimate Treasure</t>
+  </si>
+  <si>
     <t>General Science (07_CBSE)</t>
   </si>
   <si>
-    <t>Optics (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Exploration: Entering the World of Secondary Science</t>
+    <t>Cell (09_CBSE)</t>
   </si>
   <si>
     <t>The Ever-Evolving World of Science</t>
   </si>
   <si>
-    <t>Light – Reflection and Refraction</t>
+    <t>Cell: The Building Block of Life</t>
+  </si>
+  <si>
+    <t>Electricity and Magnetism (08_CBSE)</t>
+  </si>
+  <si>
+    <t>The Human Eye and the Colourful World</t>
+  </si>
+  <si>
+    <t>Electricity: Magnetic and Heating Effects</t>
   </si>
   <si>
     <t>Acid, Bases and Salts (07_CBSE)</t>
   </si>
   <si>
+    <t>Newtonian Mechanics (08_CBSE)</t>
+  </si>
+  <si>
+    <t>Tissues (09_CBSE)</t>
+  </si>
+  <si>
+    <t>Exploring Forces</t>
+  </si>
+  <si>
+    <t>Tissues in Action</t>
+  </si>
+  <si>
     <t>Exploring Substances: Acidic, Basic, and Neutral</t>
   </si>
   <si>
-    <t>Cell (09_CBSE)</t>
-  </si>
-  <si>
-    <t>The Human Eye and the Colourful World</t>
-  </si>
-  <si>
-    <t>Atomic Structure &amp; Language of Chemistry (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Cell: The Building Block of Life</t>
+    <t>Electricity and Magnetism (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>Fluid Mechanics (08_CBSE)</t>
+  </si>
+  <si>
+    <t>Pressure, Winds, Storms, and Cyclones</t>
   </si>
   <si>
     <t>Electricity and Magnetism (07_CBSE)</t>
   </si>
   <si>
-    <t>Exploring the Investigative World of Science</t>
+    <t>Newtonian Mechanics (09_CBSE)</t>
   </si>
   <si>
     <t>Electricity: Circuits and their Components</t>
   </si>
   <si>
-    <t>Tissues (09_CBSE)</t>
-  </si>
-  <si>
-    <t>Tissues in Action</t>
+    <t>Particulate Nature of Matter</t>
+  </si>
+  <si>
+    <t>Describing Motion Around Us</t>
+  </si>
+  <si>
+    <t>Magnetic Effects of Electric Current</t>
+  </si>
+  <si>
+    <t>Physical Chemistry (08_CBSE)</t>
+  </si>
+  <si>
+    <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
   </si>
   <si>
     <t>Metals and Non-metals (07_CBSE)</t>
   </si>
   <si>
-    <t>Electricity and Magnetism (10_CBSE)</t>
+    <t>Chemical Reactions and Changes (10_CBSE)</t>
   </si>
   <si>
     <t>The World of Metals and Non-metals</t>
   </si>
   <si>
-    <t>Microorganisms (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Electricity</t>
-  </si>
-  <si>
-    <t>Newtonian Mechanics (09_CBSE)</t>
-  </si>
-  <si>
-    <t>The Invisible Living World: Beyond Our Naked Eye</t>
+    <t>Physical Chemistry (09_CBSE)</t>
+  </si>
+  <si>
+    <t>Chemical Reactions and Equations</t>
+  </si>
+  <si>
+    <t>Exploring Mixtures and their Separation</t>
+  </si>
+  <si>
+    <t>The Amazing World of Solutes, Solvents, and Solutions</t>
+  </si>
+  <si>
+    <t>Optics (08_CBSE)</t>
   </si>
   <si>
     <t>Physical Chemistry (07_CBSE)</t>
   </si>
   <si>
-    <t>Describing Motion Around Us</t>
+    <t>Light: Mirrors and Lenses</t>
+  </si>
+  <si>
+    <t>Acid, Bases and Salts (10_CBSE)</t>
   </si>
   <si>
     <t>Changes Around Us: Physical and Chemical</t>
   </si>
   <si>
-    <t>Magnetic Effects of Electric Current</t>
-  </si>
-  <si>
-    <t>Physical Chemistry (09_CBSE)</t>
+    <t>Acids, Bases and Salts</t>
+  </si>
+  <si>
+    <t>How Forces Affect Motion</t>
+  </si>
+  <si>
+    <t>Keeping Time with the Skies</t>
   </si>
   <si>
     <t>Adolescence (07_CBSE)</t>
   </si>
   <si>
-    <t>Health &amp; Hygiene (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Exploring Mixtures and their Separation</t>
-  </si>
-  <si>
-    <t>Health: The Ultimate Treasure</t>
-  </si>
-  <si>
-    <t>Chemical Reactions and Changes (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Chemical Reactions and Equations</t>
-  </si>
-  <si>
-    <t>How Forces Affect Motion</t>
-  </si>
-  <si>
-    <t>Electricity and Magnetism (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Electricity: Magnetic and Heating Effects</t>
+    <t>Ecosystem (08_CBSE)</t>
+  </si>
+  <si>
+    <t>How Nature Works in Harmony</t>
   </si>
   <si>
     <t>Adolescence: A Stage of Growth and Change</t>
   </si>
   <si>
-    <t>Acid, Bases and Salts (10_CBSE)</t>
+    <t>Metallurgy &amp; Periodic Table (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Metals and Non-metals</t>
   </si>
   <si>
     <t>Work, Energy, and Simple Machines</t>
   </si>
   <si>
-    <t>Acids, Bases and Salts</t>
+    <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
   </si>
   <si>
     <t>Thermodynamics (07_CBSE)</t>
   </si>
   <si>
+    <t>Mathematics</t>
+  </si>
+  <si>
     <t>Heat Transfer in Nature</t>
   </si>
   <si>
+    <t>Carbon &amp; its Compounds (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Exponents and Logarithm (08_CBSE)</t>
+  </si>
+  <si>
     <t>Atomic Structure &amp; Language of Chemistry (09_CBSE)</t>
   </si>
   <si>
-    <t>Newtonian Mechanics (08_CBSE)</t>
+    <t>A Square and A Cube</t>
+  </si>
+  <si>
+    <t>Carbon and its Compounds</t>
   </si>
   <si>
     <t>Journey Inside the Atom</t>
   </si>
   <si>
-    <t>Metallurgy &amp; Periodic Table (10_CBSE)</t>
-  </si>
-  <si>
     <t>Newtonian Mechanics (07_CBSE)</t>
   </si>
   <si>
-    <t>Exploring Forces</t>
-  </si>
-  <si>
-    <t>Metals and Non-metals</t>
+    <t>Power Play</t>
   </si>
   <si>
     <t>Measurement of Time and Motion</t>
   </si>
   <si>
+    <t>Life Processes (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Number System (08_CBSE)</t>
+  </si>
+  <si>
+    <t>Life Processes</t>
+  </si>
+  <si>
+    <t>A Story of Numbers</t>
+  </si>
+  <si>
     <t>Atomic Foundations of Matter</t>
   </si>
   <si>
-    <t>Carbon &amp; its Compounds (10_CBSE)</t>
-  </si>
-  <si>
     <t>Life Processes (07_CBSE)</t>
   </si>
   <si>
-    <t>Fluid Mechanics (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Carbon and its Compounds</t>
-  </si>
-  <si>
     <t>Life Processes in Animals</t>
   </si>
   <si>
-    <t>Pressure, Winds, Storms, and Cyclones</t>
+    <t>Geometry (08_CBSE)</t>
+  </si>
+  <si>
+    <t>Quadrilaterals</t>
+  </si>
+  <si>
+    <t>Control and Coordination</t>
   </si>
   <si>
     <t>Waves Motion and its Propogation (09_CBSE)</t>
@@ -231,934 +294,859 @@
     <t>Sound Waves: Characteristics and Applications</t>
   </si>
   <si>
-    <t>Life Processes (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Life Processes</t>
-  </si>
-  <si>
     <t>Life Processes in Plants</t>
   </si>
   <si>
     <t>Reproduction &amp; Genetics (09_CBSE)</t>
   </si>
   <si>
+    <t>Reproduction &amp; Genetics (10_CBSE)</t>
+  </si>
+  <si>
     <t>Reproduction: How Life Continues</t>
   </si>
   <si>
-    <t>Particulate Nature of Matter</t>
+    <t>How do Organisms Reproduce?</t>
   </si>
   <si>
     <t>Optics (07_CBSE)</t>
   </si>
   <si>
+    <t>Playing with numbers (08_CBSE)</t>
+  </si>
+  <si>
     <t>Light: Shadows and Reflections</t>
   </si>
   <si>
-    <t>Control and Coordination</t>
-  </si>
-  <si>
     <t>Life Processes (09_CBSE)</t>
   </si>
   <si>
+    <t>Number Play</t>
+  </si>
+  <si>
     <t>Patterns in Life: Diversity and Classification</t>
   </si>
   <si>
-    <t>Physical Chemistry (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Reproduction &amp; Genetics (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
+    <t>Heredity</t>
+  </si>
+  <si>
+    <t>We Distribute, Yet Things Multiply</t>
+  </si>
+  <si>
+    <t>Ecosystem (10_CBSE)</t>
+  </si>
+  <si>
+    <t>General Science (09_CBSE)</t>
   </si>
   <si>
     <t>Earth, Moon, and the Sun</t>
   </si>
   <si>
-    <t>How do Organisms Reproduce?</t>
-  </si>
-  <si>
-    <t>General Science (09_CBSE)</t>
+    <t>Our Environment</t>
   </si>
   <si>
     <t>Earth as a System: Energy, Matter, and Life</t>
   </si>
   <si>
-    <t>Mathematics</t>
+    <t>Ratio &amp; Proportion (08_CBSE)</t>
+  </si>
+  <si>
+    <t>Coordinate Geometry (09_CBSE)</t>
+  </si>
+  <si>
+    <t>Number System (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Proportional Reasoning-1</t>
+  </si>
+  <si>
+    <t>Orienting Yourself: The Use of Coordinates</t>
   </si>
   <si>
     <t>Number System (07_CBSE)</t>
   </si>
   <si>
+    <t>Real Numbers</t>
+  </si>
+  <si>
     <t>Large Numbers Around Us</t>
   </si>
   <si>
-    <t>Coordinate Geometry (09_CBSE)</t>
-  </si>
-  <si>
-    <t>Heredity</t>
-  </si>
-  <si>
-    <t>Orienting Yourself: The Use of Coordinates</t>
-  </si>
-  <si>
-    <t>The Amazing World of Solutes, Solvents, and Solutions</t>
+    <t>Algebraic Expressions (09_CBSE)</t>
+  </si>
+  <si>
+    <t>Introduction to Linear Polynomials</t>
+  </si>
+  <si>
+    <t>Algebraic Expressions (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Fractions in Disguise</t>
+  </si>
+  <si>
+    <t>Polynomials</t>
   </si>
   <si>
     <t>Playing with numbers (07_CBSE)</t>
   </si>
   <si>
-    <t>Ecosystem (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Algebraic Expressions (09_CBSE)</t>
+    <t>Number System (09_CBSE)</t>
+  </si>
+  <si>
+    <t>The World of Numbers</t>
   </si>
   <si>
     <t>Arithmetic Expressions</t>
   </si>
   <si>
-    <t>Our Environment</t>
-  </si>
-  <si>
-    <t>Introduction to Linear Polynomials</t>
-  </si>
-  <si>
-    <t>Optics (08_CBSE)</t>
+    <t>Equations and Inequalities (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Mensuration (08_CBSE)</t>
+  </si>
+  <si>
+    <t>Pair of Linear Equations in Two Variables</t>
+  </si>
+  <si>
+    <t>Geometry (09_CBSE)</t>
+  </si>
+  <si>
+    <t>The Baudhayana-Pythagoras Theorem</t>
+  </si>
+  <si>
+    <t>Exploring Algebraic Identities</t>
   </si>
   <si>
     <t>Ratio &amp; Proportion (07_CBSE)</t>
   </si>
   <si>
-    <t>Light: Mirrors and Lenses</t>
-  </si>
-  <si>
-    <t>Number System (09_CBSE)</t>
-  </si>
-  <si>
-    <t>Number System (10_CBSE)</t>
-  </si>
-  <si>
     <t>A Peek Beyond the Point</t>
   </si>
   <si>
-    <t>The World of Numbers</t>
-  </si>
-  <si>
-    <t>Real Numbers</t>
+    <t>I’m Up and Down, and Round and Round</t>
+  </si>
+  <si>
+    <t>Proportional Reasoning-2</t>
+  </si>
+  <si>
+    <t>Quadratic Equations</t>
   </si>
   <si>
     <t>Equations and Inequalities (07_CBSE)</t>
   </si>
   <si>
-    <t>Geometry (09_CBSE)</t>
+    <t>Sequence and Series (10_CBSE)</t>
   </si>
   <si>
     <t>Expressions using Letter-Numbers</t>
   </si>
   <si>
-    <t>Algebraic Expressions (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Exploring Algebraic Identities</t>
-  </si>
-  <si>
-    <t>Polynomials</t>
+    <t>Arithmetic Progressions</t>
+  </si>
+  <si>
+    <t>Exploring Some Geometric Themes</t>
+  </si>
+  <si>
+    <t>Measuring Space: Perimeter and Are</t>
+  </si>
+  <si>
+    <t>Geometry (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Triangles</t>
   </si>
   <si>
     <t>Geometry (07_CBSE)</t>
   </si>
   <si>
-    <t>Keeping Time with the Skies</t>
+    <t>Statistics and Probability (08_CBSE)</t>
   </si>
   <si>
     <t>Parallel and Intersecting Lines</t>
   </si>
   <si>
-    <t>Equations and Inequalities (10_CBSE)</t>
-  </si>
-  <si>
-    <t>I’m Up and Down, and Round and Round</t>
-  </si>
-  <si>
-    <t>Pair of Linear Equations in Two Variables</t>
-  </si>
-  <si>
-    <t>Number Play</t>
-  </si>
-  <si>
-    <t>Ecosystem (08_CBSE)</t>
-  </si>
-  <si>
-    <t>How Nature Works in Harmony</t>
-  </si>
-  <si>
-    <t>Measuring Space: Perimeter and Are</t>
+    <t>Statistics and Probability (09_CBSE)</t>
+  </si>
+  <si>
+    <t>Tales by Dots and Lines</t>
+  </si>
+  <si>
+    <t>The Mathematics of Maybe: Introduction to Probability</t>
+  </si>
+  <si>
+    <t>Coordinate Geometry (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Coordinate Geometry</t>
+  </si>
+  <si>
+    <t>Algebraic Expressions (08_CBSE)</t>
+  </si>
+  <si>
+    <t>Algebra Play</t>
+  </si>
+  <si>
+    <t>Sequence and Series (09_CBSE)</t>
+  </si>
+  <si>
+    <t>Trigonometry (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Introduction to Trigonometry</t>
+  </si>
+  <si>
+    <t>Predicting What Comes Next: Exploring Sequences and Progression</t>
+  </si>
+  <si>
+    <t>Some Applications of Trigonometry</t>
   </si>
   <si>
     <t>A Tale of Three Intersecting Lines</t>
   </si>
   <si>
-    <t>Statistics and Probability (09_CBSE)</t>
-  </si>
-  <si>
-    <t>The Mathematics of Maybe: Introduction to Probability</t>
-  </si>
-  <si>
-    <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Circles</t>
   </si>
   <si>
     <t>Working with Fractions</t>
   </si>
   <si>
-    <t>Sequence and Series (09_CBSE)</t>
-  </si>
-  <si>
-    <t>Predicting What Comes Next: Exploring Sequences and Progression</t>
+    <t>Mensuration (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Areas Related to Circles</t>
   </si>
   <si>
     <t>Geometric Twins</t>
   </si>
   <si>
-    <t>Exponents and Logarithm (08_CBSE)</t>
-  </si>
-  <si>
-    <t>A Square and A Cube</t>
+    <t>Surface Areas and Volumes</t>
+  </si>
+  <si>
+    <t>Statistics and Probability (10_CBSE)</t>
   </si>
   <si>
     <t>Operations with Integers</t>
   </si>
   <si>
-    <t>Power Play</t>
+    <t>Statistics</t>
+  </si>
+  <si>
+    <t>Social Science</t>
+  </si>
+  <si>
+    <t>INTERACTION BETWEEN NATURAL AND HUMAN ENVIRONMENT (08_CBSE)</t>
+  </si>
+  <si>
+    <t>Natural Resources and Their Use</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>MEDIEVAL INDIA (08_CBSE)</t>
   </si>
   <si>
     <t>Finding Common Ground</t>
   </si>
   <si>
-    <t>Quadratic Equations</t>
+    <t>Reshaping India’s Political Map</t>
+  </si>
+  <si>
+    <t>MODERN WORLD HISTORY (10_CBSE)</t>
+  </si>
+  <si>
+    <t>The Rise of Nationalism in Europe</t>
+  </si>
+  <si>
+    <t>The Rise of the Marathas</t>
+  </si>
+  <si>
+    <t>COLONIALISM IN INDIA AND THE FREEDOM STRUGGLE (10_CBSE)</t>
   </si>
   <si>
     <t>Another Peek Beyond the Point</t>
   </si>
   <si>
-    <t>Number System (08_CBSE)</t>
-  </si>
-  <si>
-    <t>A Story of Numbers</t>
-  </si>
-  <si>
-    <t>Sequence and Series (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Arithmetic Progressions</t>
+    <t>Mensuration (09_CBSE)</t>
+  </si>
+  <si>
+    <t>Nationalism in India</t>
+  </si>
+  <si>
+    <t>COLONIALISM IN INDIA AND THE FREEDOM STRUGGLE (08_CBSE)</t>
+  </si>
+  <si>
+    <t>The Colonial Era in India</t>
+  </si>
+  <si>
+    <t>The Making of a Global World</t>
   </si>
   <si>
     <t>Statistics and Probability (07_CBSE)</t>
   </si>
   <si>
+    <t>DEMOCRACY (08_CBSE)</t>
+  </si>
+  <si>
+    <t>Universal Franchise and India’s Electoral System</t>
+  </si>
+  <si>
     <t>Connecting the Dots...</t>
   </si>
   <si>
-    <t>Geometry (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Quadrilaterals</t>
-  </si>
-  <si>
-    <t>Geometry (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Triangles</t>
+    <t>The Age of Industrialisation</t>
+  </si>
+  <si>
+    <t>INSTITUTIONS (08_CBSE)</t>
+  </si>
+  <si>
+    <t>The Parliamentary System: Legislature and Executive</t>
+  </si>
+  <si>
+    <t>Equations and Inequalities (09_CBSE)</t>
+  </si>
+  <si>
+    <t>Print Culture and the Modern World</t>
   </si>
   <si>
     <t>Constructions and Tilings</t>
   </si>
   <si>
-    <t>Mensuration (09_CBSE)</t>
-  </si>
-  <si>
-    <t>Playing with numbers (08_CBSE)</t>
+    <t>Market Mechanisms and Production (08_CBSE)</t>
+  </si>
+  <si>
+    <t>Factors of Production</t>
+  </si>
+  <si>
+    <t>GOVERNMENT (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Power-sharing</t>
+  </si>
+  <si>
+    <t>EARTH : IT'S LANDFORMS , MOVEMENT AND STRUCTURE (08_CBSE)</t>
+  </si>
+  <si>
+    <t>World Geography: Some Glimpses</t>
   </si>
   <si>
     <t>Finding the Unknown</t>
   </si>
   <si>
-    <t>Coordinate Geometry (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Coordinate Geometry</t>
-  </si>
-  <si>
-    <t>Social Science</t>
+    <t>Federalism</t>
+  </si>
+  <si>
+    <t>India’s Long Road to Independence</t>
+  </si>
+  <si>
+    <t>DISCRIMINATION (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Gender, Religion and Caste</t>
   </si>
   <si>
     <t>GEOGRAPHICAL OVERVIEW OF INDIA : PHYSICAL FEATURES, SIZE, LOCATION, AND CLIMATE (07_CBSE)</t>
   </si>
   <si>
+    <t>BUILDINGS, PAINTINGS AND BOOKS (08_CBSE)</t>
+  </si>
+  <si>
     <t>Geographical Diversity of India</t>
   </si>
   <si>
-    <t>We Distribute, Yet Things Multiply</t>
-  </si>
-  <si>
-    <t>Trigonometry (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Introduction to Trigonometry</t>
+    <t xml:space="preserve">A Journey Through Indian Architecture </t>
+  </si>
+  <si>
+    <t>DEMOCRACY (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Political Parties</t>
+  </si>
+  <si>
+    <t>INTRODUCTION (09_CBSE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Role of the Judiciary in Our Society </t>
   </si>
   <si>
     <t>EARTH’S DOMAINS AND ATMOSPHERE AND CLIMATE (07_CBSE)</t>
   </si>
   <si>
+    <t>Understanding Social Science</t>
+  </si>
+  <si>
     <t>Understanding the Weather</t>
   </si>
   <si>
-    <t>Ratio &amp; Proportion (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Equations and Inequalities (09_CBSE)</t>
-  </si>
-  <si>
-    <t>Proportional Reasoning-1</t>
-  </si>
-  <si>
-    <t>Some Applications of Trigonometry</t>
+    <t>Outcomes of Democracy</t>
+  </si>
+  <si>
+    <t>Citizenship: Rights and Duties</t>
+  </si>
+  <si>
+    <t>EARTH : IT'S LANDFORMS , MOVEMENT AND STRUCTURE (09_CBSE)</t>
+  </si>
+  <si>
+    <t>Population :Growth , Movement And Urabanisation (08_CBSE)</t>
+  </si>
+  <si>
+    <t>NATURAL AND HUMAN RESOURCES: MANAGEMENT AND SUSTAINABILITY (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Shaping of the Earth’s Surface</t>
+  </si>
+  <si>
+    <t>Dynamics of Population</t>
+  </si>
+  <si>
+    <t>Resources and Development</t>
   </si>
   <si>
     <t>Climates of India</t>
   </si>
   <si>
-    <t>Fractions in Disguise</t>
+    <t>EARTH’S DOMAINS AND ATMOSPHERE AND CLIMATE (09_CBSE)</t>
+  </si>
+  <si>
+    <t>Atmosphere and Climate</t>
+  </si>
+  <si>
+    <t>India’s Urban Landscape</t>
+  </si>
+  <si>
+    <t>Forest and Wildlife Resources</t>
   </si>
   <si>
     <t>ANCIENT INDIA (07_CBSE)</t>
   </si>
   <si>
-    <t>Circles</t>
+    <t>CIVILISATIONS (09_CBSE)</t>
+  </si>
+  <si>
+    <t>Hydrosphere: Water Systems and their Dynamics (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Early Humans and Beginning of Civilisation</t>
+  </si>
+  <si>
+    <t>Cultural Currents: 13th to 17th Centuries</t>
   </si>
   <si>
     <t>New Beginnings: Cities and States</t>
   </si>
   <si>
-    <t>Mensuration (08_CBSE)</t>
-  </si>
-  <si>
-    <t>The Baudhayana-Pythagoras Theorem</t>
-  </si>
-  <si>
-    <t>Mensuration (10_CBSE)</t>
+    <t>Water Resources</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>ANCIENT INDIA (09_CBSE)</t>
+  </si>
+  <si>
+    <t>PROSE (08_CBSE)</t>
+  </si>
+  <si>
+    <t>AGRICULTURE (10_CBSE)</t>
+  </si>
+  <si>
+    <t>State and Society up to 1000 CE</t>
+  </si>
+  <si>
+    <t>The Wit that Won Hearts</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
   </si>
   <si>
     <t>The Rise of Empires</t>
   </si>
   <si>
-    <t>Areas Related to Circles</t>
-  </si>
-  <si>
-    <t>Proportional Reasoning-2</t>
+    <t>DEMOCRACY (09_CBSE)</t>
+  </si>
+  <si>
+    <t>NATURAL AND HUMAN RESOURCES : MANAGEMENT AND SUSTAINABILITY (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Democracy</t>
+  </si>
+  <si>
+    <t>Minerals and Energy Resources</t>
+  </si>
+  <si>
+    <t>POEM (08_CBSE)</t>
+  </si>
+  <si>
+    <t>A Concrete Example</t>
+  </si>
+  <si>
+    <t>INDUSTRIES (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Elections</t>
+  </si>
+  <si>
+    <t>Manufacturing Industries</t>
   </si>
   <si>
     <t>The Age of Reorganisation</t>
   </si>
   <si>
-    <t>Exploring Some Geometric Themes</t>
-  </si>
-  <si>
-    <t>Surface Areas and Volumes</t>
+    <t>DRAMA (08_CBSE)</t>
+  </si>
+  <si>
+    <t>Wisdom Paves the Way</t>
+  </si>
+  <si>
+    <t>LIFELINES OF NATIONAL ECONOMY (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Lifelines of National Economy</t>
+  </si>
+  <si>
+    <t>Introduction to Economics &amp; Economic Systems (09_CBSE)</t>
+  </si>
+  <si>
+    <t>A Tale of Valour: Major Somnath Sharma and the Battle of Badgam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building Blocks in Economics: The Problem of Choice </t>
+  </si>
+  <si>
+    <t>Development , Globalisation and Consumer Awareness (10_CBSE)</t>
   </si>
   <si>
     <t>The Gupta Era: An Age of Tireless Creativity</t>
   </si>
   <si>
-    <t>Statistics and Probability (08_CBSE)</t>
-  </si>
-  <si>
-    <t>INTRODUCTION (09_CBSE)</t>
-  </si>
-  <si>
-    <t>Tales by Dots and Lines</t>
-  </si>
-  <si>
-    <t>Statistics and Probability (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Statistics</t>
+    <t>Development</t>
+  </si>
+  <si>
+    <t>Somebody’s Mother</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Price Puzzle: What Drives the Market </t>
+  </si>
+  <si>
+    <t>Introduction to Economics &amp; Economic Systems (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Sectors of the Indian Economy</t>
   </si>
   <si>
     <t>How the Land Becomes Sacred</t>
   </si>
   <si>
-    <t>Social Science: Meaning, Scope and Importance</t>
-  </si>
-  <si>
-    <t>Algebraic Expressions (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Algebra Play</t>
+    <t>Money, Banking, and Credit (10_CBSE)</t>
+  </si>
+  <si>
+    <t>Money and Credit</t>
   </si>
   <si>
     <t>GOVERNMENT (07_CBSE)</t>
   </si>
   <si>
-    <t>EARTH : IT'S LANDFORMS , MOVEMENT AND STRUCTURE (09_CBSE)</t>
-  </si>
-  <si>
-    <t>Probability</t>
+    <t>Globalisation and the Indian economy (10_CBSE)</t>
   </si>
   <si>
     <t>From the Rulers to the Ruled: Types of Governments</t>
   </si>
   <si>
-    <t>Landforms: Earth's Living Canvas</t>
+    <t>Globalisation and the Indian Economy.</t>
+  </si>
+  <si>
+    <t>Verghese Kurien— I Too Had A Dream</t>
   </si>
   <si>
     <t>CONSTITUTION (07_CBSE)</t>
   </si>
   <si>
-    <t>EARTH’S DOMAINS AND ATMOSPHERE AND CLIMATE (09_CBSE)</t>
-  </si>
-  <si>
-    <t>MODERN WORLD HISTORY (10_CBSE)</t>
+    <t>Consumer Rights .</t>
   </si>
   <si>
     <t>The Constitution of India — An Introduction</t>
   </si>
   <si>
-    <t>The Dynamic Atmosphere and Changing Climate</t>
-  </si>
-  <si>
-    <t>The Rise of Nationalism in Europe</t>
+    <t>PROSE (10_CBSE)</t>
   </si>
   <si>
     <t>Money, Banking, and Credit (07_CBSE)</t>
   </si>
   <si>
-    <t>CIVILISATIONS (09_CBSE)</t>
-  </si>
-  <si>
-    <t>Area</t>
-  </si>
-  <si>
     <t>From Barter to Money</t>
   </si>
   <si>
-    <t>COLONIALISM IN INDIA AND THE FREEDOM STRUGGLE (10_CBSE)</t>
-  </si>
-  <si>
-    <t>The Earliest People: The Stone Age</t>
-  </si>
-  <si>
-    <t>Nationalism in India</t>
+    <t>A Letter to God</t>
+  </si>
+  <si>
+    <t>PROSE (09_CBSE)</t>
+  </si>
+  <si>
+    <t>POEM (10_CBSE)</t>
   </si>
   <si>
     <t>Market Mechanisms and Production (07_CBSE)</t>
   </si>
   <si>
-    <t>Harappan and Contemporary Mesopotamian Civilisations</t>
+    <t>Dust of Snow</t>
+  </si>
+  <si>
+    <t>The Case of the Fifth Word</t>
   </si>
   <si>
     <t>Understanding Markets</t>
   </si>
   <si>
-    <t>The Making of a Global World</t>
-  </si>
-  <si>
-    <t>INTERACTION BETWEEN NATURAL AND HUMAN ENVIRONMENT (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Egyptian and Chinese Civilisations</t>
+    <t>Fire and Ice</t>
   </si>
   <si>
     <t>AGRICULTURE (07_CBSE)</t>
   </si>
   <si>
-    <t>Natural Resources and Their Use</t>
-  </si>
-  <si>
-    <t>The Age of Industrialisation</t>
+    <t>How I Taught My Grandmother to Read</t>
+  </si>
+  <si>
+    <t>The Magic Brush of Dreams</t>
   </si>
   <si>
     <t>The Story of Indian Farming</t>
   </si>
   <si>
-    <t>VEDIC PERIOD (09_CBSE)</t>
-  </si>
-  <si>
-    <t>MEDIEVAL INDIA (08_CBSE)</t>
-  </si>
-  <si>
-    <t>The Vedic Age</t>
-  </si>
-  <si>
-    <t>Reshaping India’s Political Map</t>
-  </si>
-  <si>
-    <t>Print Culture and the Modern World</t>
-  </si>
-  <si>
-    <t>ANCIENT INDIA (09_CBSE)</t>
+    <t>Spectacular Wonders</t>
   </si>
   <si>
     <t>India and Her Neighbours</t>
   </si>
   <si>
-    <t>Rise of Kingdoms, and Republics, and Early Empires</t>
-  </si>
-  <si>
-    <t>GOVERNMENT (10_CBSE)</t>
-  </si>
-  <si>
-    <t>The Rise of the Marathas</t>
-  </si>
-  <si>
-    <t>Power-sharing</t>
-  </si>
-  <si>
-    <t>DEMOCRACY (09_CBSE)</t>
-  </si>
-  <si>
-    <t>COLONIALISM IN INDIA AND THE FREEDOM STRUGGLE (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Understanding Democracy</t>
+    <t>POEM (09_CBSE)</t>
+  </si>
+  <si>
+    <t>Nelson Mandela: Long Walk to Freedom</t>
+  </si>
+  <si>
+    <t>Bharat Our Land</t>
+  </si>
+  <si>
+    <t>The Cherry Tree</t>
   </si>
   <si>
     <t>Empires and Kingdoms: 6th to 10th Centuries</t>
   </si>
   <si>
-    <t>The Colonial Era in India</t>
-  </si>
-  <si>
-    <t>Federalism</t>
-  </si>
-  <si>
-    <t>DEMOCRACY (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Elections in Indian Democracy</t>
-  </si>
-  <si>
-    <t>Universal Franchise and India’s Electoral System</t>
-  </si>
-  <si>
-    <t>DISCRIMINATION (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Gender, Religion and Caste</t>
+    <t>A Tiger in the Zoo</t>
+  </si>
+  <si>
+    <t>The Pot Maker</t>
+  </si>
+  <si>
+    <t>Harvest Hymn</t>
   </si>
   <si>
     <t>Turning Tides: 11th and 12th Centuries</t>
   </si>
   <si>
-    <t>Introduction to Economics &amp; Economic Systems (09_CBSE)</t>
-  </si>
-  <si>
-    <t>INSTITUTIONS (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Why Choices Matter: The Basics of Economics</t>
-  </si>
-  <si>
-    <t>The Parliamentary System: Legislature and Executive</t>
-  </si>
-  <si>
-    <t>DEMOCRACY (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Political Parties</t>
+    <t>Two Stories about Flying</t>
+  </si>
+  <si>
+    <t>Waiting for the Rain</t>
+  </si>
+  <si>
+    <t>Gifts of Grace: Honouring Our Vocations</t>
+  </si>
+  <si>
+    <t>How to Tell Wild Animals</t>
   </si>
   <si>
     <t>DISCRIMINATION (07_CBSE)</t>
   </si>
   <si>
+    <t>Feathered Friend</t>
+  </si>
+  <si>
     <t>India, a Home to Many</t>
   </si>
   <si>
-    <t>Market Mechanisms and Production (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Why Prices Change: The Story of Demand and Supply</t>
-  </si>
-  <si>
-    <t>Factors of Production</t>
-  </si>
-  <si>
-    <t>Outcomes of Democracy</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>EARTH : IT'S LANDFORMS , MOVEMENT AND STRUCTURE (08_CBSE)</t>
+    <t>Winds of Change</t>
+  </si>
+  <si>
+    <t>The Ball Poem</t>
+  </si>
+  <si>
+    <t>Canvas of Soil</t>
+  </si>
+  <si>
+    <t>From the Diary of Anne Frank</t>
+  </si>
+  <si>
+    <t>Magnifying Glass</t>
   </si>
   <si>
     <t>The State, the Government, and You</t>
   </si>
   <si>
-    <t>World Geography: Some Glimpses</t>
-  </si>
-  <si>
-    <t>NATURAL AND HUMAN RESOURCES: MANAGEMENT AND SUSTAINABILITY (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Resources and Development</t>
-  </si>
-  <si>
-    <t>PROSE (09_CBSE)</t>
-  </si>
-  <si>
-    <t>How I Taught My Grandmother to Read</t>
-  </si>
-  <si>
-    <t>India’s Long Road to Independence</t>
+    <t>Vitamin-M</t>
+  </si>
+  <si>
+    <t>Amanda!</t>
+  </si>
+  <si>
+    <t>Bibha Chowdhuri: The Beam of Light that Lit the Path for Women in Indian Science</t>
+  </si>
+  <si>
+    <t>I Cannot Remember My Mother</t>
+  </si>
+  <si>
+    <t>Glimpses of India</t>
   </si>
   <si>
     <t>Development , Globalisation and Consumer Awareness (07_CBSE)</t>
   </si>
   <si>
+    <t>DRAMA (09_CBSE)</t>
+  </si>
+  <si>
     <t>Infrastructure: Engine of India’s Development</t>
   </si>
   <si>
-    <t>POEM (09_CBSE)</t>
-  </si>
-  <si>
-    <t>Forest and Wildlife Resources</t>
-  </si>
-  <si>
-    <t>Bharat Our Land</t>
-  </si>
-  <si>
-    <t>BUILDINGS, PAINTINGS AND BOOKS (08_CBSE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Journey Through Indian Architecture </t>
-  </si>
-  <si>
-    <t>Hydrosphere: Water Systems and their Dynamics (10_CBSE)</t>
-  </si>
-  <si>
-    <t>The Pot Maker</t>
-  </si>
-  <si>
-    <t>Water Resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Role of the Judiciary in Our Society </t>
+    <t>The Trees</t>
+  </si>
+  <si>
+    <t>The World of Limitless Possibilities</t>
+  </si>
+  <si>
+    <t>Mijbil the Otter</t>
+  </si>
+  <si>
+    <t>Nine Gold Medals</t>
+  </si>
+  <si>
+    <t>Fog</t>
   </si>
   <si>
     <t>Banks and the Magic of Finance</t>
   </si>
   <si>
-    <t>AGRICULTURE (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Gifts of Grace: Honouring Our Vocations</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>Citizenship: Rights and Duties</t>
-  </si>
-  <si>
-    <t>Winds of Change</t>
-  </si>
-  <si>
-    <t>NATURAL AND HUMAN RESOURCES : MANAGEMENT AND SUSTAINABILITY (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Population :Growth , Movement And Urabanisation (08_CBSE)</t>
+    <t>Twin Melodies</t>
+  </si>
+  <si>
+    <t>Madam Rides the Bus</t>
+  </si>
+  <si>
+    <t>A Friend Found in Music</t>
   </si>
   <si>
     <t>PROSE (07_CBSE)</t>
   </si>
   <si>
-    <t>Dynamics of Population</t>
-  </si>
-  <si>
-    <t>Minerals and Energy Resources</t>
+    <t>The Tale of Custard the Dragon</t>
+  </si>
+  <si>
+    <t>Carrier of Words</t>
   </si>
   <si>
     <t>The Day the River Spoke</t>
   </si>
   <si>
-    <t>Canvas of Soil</t>
-  </si>
-  <si>
-    <t>INDUSTRIES (10_CBSE)</t>
-  </si>
-  <si>
-    <t>India’s Urban Landscape</t>
-  </si>
-  <si>
-    <t>Manufacturing Industries</t>
+    <t>The Sermon at Benares</t>
+  </si>
+  <si>
+    <t>Words</t>
+  </si>
+  <si>
+    <t>For Anne Gregory</t>
   </si>
   <si>
     <t>POEM (07_CBSE)</t>
   </si>
   <si>
-    <t>Vitamin-M</t>
-  </si>
-  <si>
     <t>Try Again</t>
   </si>
   <si>
-    <t>LIFELINES OF NATIONAL ECONOMY (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Cultural Currents: 13th to 17th Centuries</t>
-  </si>
-  <si>
-    <t>Lifelines of National Economy</t>
-  </si>
-  <si>
-    <t>I Cannot Remember My Mother</t>
+    <t>Follow That Dream</t>
+  </si>
+  <si>
+    <t>DRAMA (10_CBSE)</t>
+  </si>
+  <si>
+    <t>The Proposal</t>
+  </si>
+  <si>
+    <t>A Triumph of Surgery</t>
   </si>
   <si>
     <t>Three Days to See</t>
   </si>
   <si>
-    <t>Development , Globalisation and Consumer Awareness (10_CBSE)</t>
-  </si>
-  <si>
-    <t>PROSE (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Development</t>
-  </si>
-  <si>
-    <t>DRAMA (09_CBSE)</t>
-  </si>
-  <si>
-    <t>The Wit that Won Hearts</t>
-  </si>
-  <si>
-    <t>The World of Limitless Possibilities</t>
+    <t>Believe in Yourself</t>
+  </si>
+  <si>
+    <t>The Thief’s Story</t>
   </si>
   <si>
     <t>Animals, Birds, and Dr. Dolittle</t>
   </si>
   <si>
-    <t>Introduction to Economics &amp; Economic Systems (10_CBSE)</t>
-  </si>
-  <si>
-    <t>POEM (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Sectors of the Indian Economy</t>
-  </si>
-  <si>
-    <t>A Concrete Example</t>
-  </si>
-  <si>
-    <t>DRAMA (08_CBSE)</t>
-  </si>
-  <si>
-    <t>Money, Banking, and Credit (10_CBSE)</t>
+    <t>The Midnight Visitor</t>
+  </si>
+  <si>
+    <t>A Question of Trust</t>
   </si>
   <si>
     <t>A Funny Man</t>
   </si>
   <si>
-    <t>Wisdom Paves the Way</t>
-  </si>
-  <si>
-    <t>Money and Credit</t>
-  </si>
-  <si>
-    <t>Nine Gold Medals</t>
-  </si>
-  <si>
-    <t>Globalisation and the Indian economy (10_CBSE)</t>
-  </si>
-  <si>
-    <t>A Tale of Valour: Major Somnath Sharma and the Battle of Badgam</t>
+    <t>Footprints without Feet</t>
+  </si>
+  <si>
+    <t>The Making of a Scientist</t>
   </si>
   <si>
     <t>DRAMA (07_CBSE)</t>
   </si>
   <si>
-    <t>Globalisation and the Indian Economy.</t>
-  </si>
-  <si>
     <t>Say the Right Thing</t>
   </si>
   <si>
-    <t>Twin Melodies</t>
-  </si>
-  <si>
-    <t>Somebody’s Mother</t>
-  </si>
-  <si>
-    <t>Consumer Rights .</t>
+    <t>The Necklace</t>
+  </si>
+  <si>
+    <t>Bholi</t>
   </si>
   <si>
     <t>My Brother’s Great Invention</t>
   </si>
   <si>
-    <t>A Friend Found in Music</t>
-  </si>
-  <si>
-    <t>Verghese Kurien— I Too Had A Dream</t>
-  </si>
-  <si>
-    <t>PROSE (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Carrier of Words</t>
+    <t>The Book That Saved the Earth</t>
   </si>
   <si>
     <t>Paper Boats</t>
   </si>
   <si>
-    <t>The Case of the Fifth Word</t>
-  </si>
-  <si>
-    <t>A Letter to God</t>
-  </si>
-  <si>
-    <t>Words</t>
-  </si>
-  <si>
     <t>North, South, East, West</t>
   </si>
   <si>
-    <t>POEM (10_CBSE)</t>
-  </si>
-  <si>
-    <t>Follow That Dream</t>
-  </si>
-  <si>
-    <t>Dust of Snow</t>
-  </si>
-  <si>
     <t>The Tunnel</t>
   </si>
   <si>
-    <t>The Magic Brush of Dreams</t>
-  </si>
-  <si>
-    <t>Believe in Yourself</t>
-  </si>
-  <si>
-    <t>Fire and Ice</t>
-  </si>
-  <si>
-    <t>Spectacular Wonders</t>
-  </si>
-  <si>
     <t>Travel</t>
   </si>
   <si>
-    <t>Nelson Mandela: Long Walk to Freedom</t>
-  </si>
-  <si>
-    <t>The Cherry Tree</t>
-  </si>
-  <si>
-    <t>A Tiger in the Zoo</t>
-  </si>
-  <si>
     <t>Conquering the Summit</t>
   </si>
   <si>
-    <t>Harvest Hymn</t>
-  </si>
-  <si>
-    <t>Two Stories about Flying</t>
-  </si>
-  <si>
     <t>A Homage to Our Brave Soldiers</t>
   </si>
   <si>
-    <t>Waiting for the Rain</t>
-  </si>
-  <si>
-    <t>How to Tell Wild Animals</t>
-  </si>
-  <si>
-    <t>Feathered Friend</t>
-  </si>
-  <si>
     <t>My Dear Soldiers</t>
   </si>
   <si>
-    <t>The Ball Poem</t>
-  </si>
-  <si>
-    <t>Magnifying Glass</t>
-  </si>
-  <si>
     <t>COMIC (07_CBSE)</t>
   </si>
   <si>
     <t>Rani Abbakka</t>
-  </si>
-  <si>
-    <t>From the Diary of Anne Frank</t>
-  </si>
-  <si>
-    <t>Bibha Chowdhuri: The Beam of Light that Lit the Path for Women in Indian Science</t>
-  </si>
-  <si>
-    <t>Amanda!</t>
-  </si>
-  <si>
-    <t>Glimpses of India</t>
-  </si>
-  <si>
-    <t>The Trees</t>
-  </si>
-  <si>
-    <t>Mijbil the Otter</t>
-  </si>
-  <si>
-    <t>Fog</t>
-  </si>
-  <si>
-    <t>Madam Rides the Bus</t>
-  </si>
-  <si>
-    <t>The Tale of Custard the Dragon</t>
-  </si>
-  <si>
-    <t>The Sermon at Benares</t>
-  </si>
-  <si>
-    <t>For Anne Gregory</t>
-  </si>
-  <si>
-    <t>DRAMA (10_CBSE)</t>
-  </si>
-  <si>
-    <t>The Proposal</t>
-  </si>
-  <si>
-    <t>A Triumph of Surgery</t>
-  </si>
-  <si>
-    <t>The Thief’s Story</t>
-  </si>
-  <si>
-    <t>The Midnight Visitor</t>
-  </si>
-  <si>
-    <t>A Question of Trust</t>
-  </si>
-  <si>
-    <t>Footprints without Feet</t>
-  </si>
-  <si>
-    <t>The Making of a Scientist</t>
-  </si>
-  <si>
-    <t>The Necklace</t>
-  </si>
-  <si>
-    <t>Bholi</t>
-  </si>
-  <si>
-    <t>The Book That Saved the Earth</t>
   </si>
   <si>
     <t>General Science (06_CBSE)</t>
@@ -1416,7 +1404,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1429,6 +1417,12 @@
         <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -1436,7 +1430,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1452,12 +1446,15 @@
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -1497,7 +1494,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Aathira Thottathil" id="{2253cc35-df39-46fa-bbc2-3157e2661212}" providerId="google-sheets"/>
+  <x18tc:person displayName="Aathira Thottathil" id="{60491248-ae52-49d4-9c2d-2730d7789fee}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1697,7 +1694,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A45" dT="2026-06-22T11:29:13.00" personId="{2253cc35-df39-46fa-bbc2-3157e2661212}" id="{3e9cbbfc-2fbe-4d04-a43d-71016acf410c}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-06-22T11:29:13.00" personId="{60491248-ae52-49d4-9c2d-2730d7789fee}" id="{ae5cab91-4a47-4fb0-885d-5f477d8f6cf1}" done="0">
     <x18tc:text xml:space="preserve">Part 2 Textbook for class 9 not available</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1752,10 +1749,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -1763,10 +1760,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -1774,10 +1771,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -1785,10 +1782,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -1796,10 +1793,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -1807,10 +1804,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
@@ -1818,10 +1815,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -1829,10 +1826,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -1840,10 +1837,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -1851,10 +1848,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12">
@@ -1862,10 +1859,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -1873,10 +1870,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1884,21 +1881,21 @@
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D15" s="3">
         <v>10.0</v>
@@ -1906,13 +1903,13 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3">
         <v>10.0</v>
@@ -1920,13 +1917,13 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D17" s="3">
         <v>10.0</v>
@@ -1934,13 +1931,13 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3">
         <v>10.0</v>
@@ -1948,13 +1945,13 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3">
         <v>10.0</v>
@@ -1962,13 +1959,13 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D20" s="3">
         <v>10.0</v>
@@ -1976,13 +1973,13 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3">
         <v>10.0</v>
@@ -1990,13 +1987,13 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D22" s="3">
         <v>10.0</v>
@@ -2004,13 +2001,13 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D23" s="3">
         <v>10.0</v>
@@ -2018,13 +2015,13 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="D24" s="3">
         <v>10.0</v>
@@ -2032,13 +2029,13 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D25" s="3">
         <v>10.0</v>
@@ -2046,13 +2043,13 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="D26" s="3">
         <v>10.0</v>
@@ -2060,13 +2057,13 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="D27" s="3">
         <v>10.0</v>
@@ -2074,13 +2071,13 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D28" s="3">
         <v>10.0</v>
@@ -2088,556 +2085,557 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>249</v>
+        <v>215</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>262</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>268</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>280</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>289</v>
+        <v>255</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>301</v>
+        <v>265</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>303</v>
+        <v>266</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>306</v>
+        <v>268</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>309</v>
+        <v>269</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>311</v>
+        <v>271</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>314</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>311</v>
+        <v>271</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>326</v>
+        <v>235</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>331</v>
+        <v>235</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>335</v>
+        <v>235</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>338</v>
+        <v>235</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>340</v>
+        <v>235</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>343</v>
+        <v>235</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>346</v>
+        <v>235</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>349</v>
+        <v>235</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>353</v>
+        <v>235</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>355</v>
+        <v>235</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>356</v>
+        <v>235</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>357</v>
+        <v>235</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C63" s="9" t="s">
-        <v>358</v>
+        <v>235</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B64" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C64" s="10" t="s">
         <v>329</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>360</v>
+        <v>235</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>361</v>
+        <v>235</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>362</v>
+        <v>235</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>363</v>
+        <v>235</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>365</v>
+        <v>235</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>366</v>
+        <v>235</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>367</v>
+        <v>235</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>368</v>
+        <v>235</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>369</v>
+        <v>235</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>370</v>
+        <v>235</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>371</v>
+        <v>235</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>372</v>
+        <v>235</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>373</v>
+        <v>235</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>374</v>
+        <v>235</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>361</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -2687,10 +2685,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2698,10 +2696,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -2709,10 +2707,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -2720,10 +2718,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -2731,10 +2729,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -2742,10 +2740,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
@@ -2753,10 +2751,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -2764,10 +2762,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -2775,10 +2773,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -2786,10 +2784,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -2797,10 +2795,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
@@ -2808,10 +2806,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2819,510 +2817,476 @@
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" s="5"/>
+        <v>124</v>
+      </c>
+      <c r="C23" s="6"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="5"/>
+        <v>112</v>
+      </c>
+      <c r="C24" s="6"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25" s="5"/>
+        <v>124</v>
+      </c>
+      <c r="C25" s="6"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C26" s="5"/>
+        <v>178</v>
+      </c>
+      <c r="C26" s="6"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C27" s="5"/>
+        <v>124</v>
+      </c>
+      <c r="C27" s="6"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C28" s="5"/>
+        <v>178</v>
+      </c>
+      <c r="C28" s="6"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C29" s="5"/>
+        <v>190</v>
+      </c>
+      <c r="C29" s="6"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C30" s="5"/>
+        <v>178</v>
+      </c>
+      <c r="C30" s="6"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C31" s="5"/>
+        <v>143</v>
+      </c>
+      <c r="C31" s="6"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C32" s="5"/>
+        <v>143</v>
+      </c>
+      <c r="C32" s="6"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C33" s="5"/>
+        <v>143</v>
+      </c>
+      <c r="C33" s="6"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>184</v>
+        <v>166</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>191</v>
+        <v>166</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>196</v>
+        <v>166</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>203</v>
+        <v>166</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>206</v>
+        <v>166</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>210</v>
+        <v>166</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>217</v>
+        <v>166</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>222</v>
+        <v>166</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>228</v>
+        <v>166</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>233</v>
+      <c r="A43" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>240</v>
+      <c r="A44" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>247</v>
+      <c r="A45" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>257</v>
+      <c r="A46" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="s">
-        <v>250</v>
+      <c r="A47" s="9" t="s">
+        <v>235</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="s">
-        <v>250</v>
+      <c r="A48" s="9" t="s">
+        <v>235</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>267</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="s">
-        <v>250</v>
+      <c r="A49" s="9" t="s">
+        <v>235</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="s">
-        <v>250</v>
+      <c r="A50" s="9" t="s">
+        <v>235</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="s">
-        <v>250</v>
+      <c r="A51" s="9" t="s">
+        <v>235</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>261</v>
+        <v>323</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="C55" s="3" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="s">
-        <v>250</v>
+      <c r="A56" s="9" t="s">
+        <v>235</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="s">
-        <v>250</v>
+      <c r="A57" s="9" t="s">
+        <v>235</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="s">
-        <v>250</v>
+      <c r="A58" s="9" t="s">
+        <v>235</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId4"/>
-  <legacyDrawing r:id="rId5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3376,10 +3340,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3387,10 +3351,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -3398,10 +3362,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -3409,10 +3373,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -3420,10 +3384,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -3431,10 +3395,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -3442,10 +3406,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -3453,10 +3417,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -3464,10 +3428,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -3475,10 +3439,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -3486,10 +3450,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>111</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -3497,10 +3461,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>118</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -3508,494 +3472,494 @@
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>147</v>
+        <v>92</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>147</v>
+        <v>92</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>154</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>161</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>169</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>175</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>180</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>200</v>
+        <v>122</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>212</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>224</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>227</v>
+        <v>180</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>230</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>232</v>
+        <v>184</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>241</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>248</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>251</v>
+        <v>197</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>253</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>227</v>
+        <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>264</v>
+        <v>205</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>265</v>
+        <v>207</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>269</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>232</v>
+        <v>184</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>274</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>277</v>
+        <v>218</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>279</v>
+        <v>221</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>277</v>
+        <v>218</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>284</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>290</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>298</v>
+        <v>240</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>302</v>
+        <v>247</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>304</v>
+        <v>248</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>305</v>
+        <v>253</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>308</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>312</v>
+        <v>258</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>302</v>
+        <v>247</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>317</v>
+        <v>263</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>321</v>
+        <v>274</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>325</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>302</v>
+        <v>247</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>333</v>
+        <v>291</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>336</v>
+        <v>293</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>339</v>
+        <v>298</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>302</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>345</v>
+        <v>305</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>347</v>
+        <v>309</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>302</v>
+        <v>247</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>350</v>
+        <v>315</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>354</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -4049,10 +4013,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -4060,10 +4024,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -4071,10 +4035,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -4082,10 +4046,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -4093,10 +4057,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -4104,10 +4068,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -4115,10 +4079,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -4126,10 +4090,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -4137,10 +4101,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -4148,10 +4112,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12">
@@ -4159,10 +4123,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -4170,560 +4134,560 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>140</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>148</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>153</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>157</v>
+        <v>212</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>158</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>157</v>
+        <v>212</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>163</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>167</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>171</v>
+        <v>242</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>174</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>177</v>
+        <v>261</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>183</v>
+        <v>267</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>187</v>
+        <v>270</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>190</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>192</v>
+        <v>275</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>195</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>201</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>205</v>
+        <v>284</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>207</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>211</v>
+        <v>289</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>214</v>
+        <v>292</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>221</v>
+        <v>294</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>229</v>
+        <v>299</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>237</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>245</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>187</v>
+        <v>270</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>252</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>259</v>
+        <v>322</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>260</v>
+        <v>324</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>270</v>
+        <v>330</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>281</v>
+        <v>337</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>288</v>
+        <v>342</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>293</v>
+        <v>347</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>307</v>
+        <v>353</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>313</v>
+        <v>356</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>315</v>
+        <v>357</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>319</v>
+        <v>360</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -4777,10 +4741,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3">
@@ -4788,10 +4752,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4">
@@ -4799,10 +4763,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5">
@@ -4810,10 +4774,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6">
@@ -4821,10 +4785,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7">
@@ -4832,10 +4796,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8">
@@ -4843,10 +4807,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -4854,10 +4818,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10">
@@ -4865,10 +4829,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11">
@@ -4876,10 +4840,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12">
@@ -4887,10 +4851,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13">
@@ -4898,450 +4862,450 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>
